--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-authoring-device.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-authoring-device.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-17T15:26:54+00:00</t>
+    <t>2025-01-23T13:26:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-authoring-device.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-authoring-device.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-23T13:26:37+00:00</t>
+    <t>2025-01-24T17:22:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-authoring-device.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-authoring-device.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-24T17:22:23+00:00</t>
+    <t>2025-01-29T14:25:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-authoring-device.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-authoring-device.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-29T14:25:50+00:00</t>
+    <t>2025-01-29T15:50:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-authoring-device.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-authoring-device.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-29T15:50:40+00:00</t>
+    <t>2025-01-30T15:03:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-authoring-device.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-authoring-device.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-30T15:03:39+00:00</t>
+    <t>2025-01-31T08:45:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-authoring-device.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-authoring-device.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-31T08:45:39+00:00</t>
+    <t>2025-02-18T10:06:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-authoring-device.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-authoring-device.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="564" uniqueCount="139">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="566" uniqueCount="141">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T10:06:11+00:00</t>
+    <t>2025-02-18T11:00:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -81,7 +81,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>authoringDevice contient les informations complémentaires si l’auteur est un système.</t>
+    <t>L'élément de l'en-tête du CDA authoringDevice contient les informations complémentaires si l’auteur est un système.</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -426,10 +426,16 @@
 </t>
   </si>
   <si>
+    <t>Nom du modèle du système.</t>
+  </si>
+  <si>
     <t>http://terminology.hl7.org/ValueSet/v3-ManufacturerModelNameExample</t>
   </si>
   <si>
     <t>AuthoringDevice.softwareName</t>
+  </si>
+  <si>
+    <t>Nom du système.</t>
   </si>
   <si>
     <t>http://terminology.hl7.org/ValueSet/v3-SoftwareNameExample</t>
@@ -2236,7 +2242,9 @@
       <c r="K15" t="s" s="2">
         <v>133</v>
       </c>
-      <c r="L15" s="2"/>
+      <c r="L15" t="s" s="2">
+        <v>134</v>
+      </c>
       <c r="M15" s="2"/>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
@@ -2267,7 +2275,7 @@
       </c>
       <c r="Y15" s="2"/>
       <c r="Z15" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>74</v>
@@ -2305,10 +2313,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -2333,7 +2341,9 @@
       <c r="K16" t="s" s="2">
         <v>133</v>
       </c>
-      <c r="L16" s="2"/>
+      <c r="L16" t="s" s="2">
+        <v>137</v>
+      </c>
       <c r="M16" s="2"/>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
@@ -2364,25 +2374,25 @@
       </c>
       <c r="Y16" s="2"/>
       <c r="Z16" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="AA16" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB16" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC16" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD16" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE16" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF16" t="s" s="2">
         <v>136</v>
-      </c>
-      <c r="AA16" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB16" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC16" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD16" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE16" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF16" t="s" s="2">
-        <v>135</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>80</v>
@@ -2402,10 +2412,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -2428,7 +2438,7 @@
         <v>74</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="L17" s="2"/>
       <c r="M17" s="2"/>
@@ -2481,7 +2491,7 @@
         <v>74</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>80</v>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-authoring-device.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-authoring-device.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T11:00:40+00:00</t>
+    <t>2025-02-18T15:10:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-authoring-device.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-authoring-device.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T15:10:02+00:00</t>
+    <t>2025-02-18T15:17:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-authoring-device.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-authoring-device.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T15:17:48+00:00</t>
+    <t>2025-02-18T15:18:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-authoring-device.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-authoring-device.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T15:18:09+00:00</t>
+    <t>2025-02-18T15:18:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-authoring-device.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-authoring-device.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T15:18:38+00:00</t>
+    <t>2025-02-18T15:24:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-authoring-device.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-authoring-device.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T15:24:54+00:00</t>
+    <t>2025-02-18T15:28:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-authoring-device.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-authoring-device.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T15:28:32+00:00</t>
+    <t>2025-02-18T15:29:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-authoring-device.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-authoring-device.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T15:29:38+00:00</t>
+    <t>2025-02-18T15:30:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-authoring-device.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-authoring-device.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T15:30:04+00:00</t>
+    <t>2025-02-18T15:30:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-authoring-device.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-authoring-device.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T15:30:23+00:00</t>
+    <t>2025-02-18T15:30:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-authoring-device.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-authoring-device.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T15:30:53+00:00</t>
+    <t>2025-02-20T13:34:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-authoring-device.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-authoring-device.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T13:34:17+00:00</t>
+    <t>2025-02-20T13:46:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-authoring-device.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-authoring-device.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T13:46:00+00:00</t>
+    <t>2025-02-20T13:48:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-authoring-device.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-authoring-device.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T13:48:47+00:00</t>
+    <t>2025-02-20T13:50:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-authoring-device.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-authoring-device.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T13:50:16+00:00</t>
+    <t>2025-02-20T13:50:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-authoring-device.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-authoring-device.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T13:50:51+00:00</t>
+    <t>2025-02-20T13:51:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-authoring-device.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-authoring-device.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T13:51:52+00:00</t>
+    <t>2025-02-20T13:53:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-authoring-device.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-authoring-device.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T13:53:17+00:00</t>
+    <t>2025-02-20T13:53:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-authoring-device.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-authoring-device.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T13:53:53+00:00</t>
+    <t>2025-02-20T14:37:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-authoring-device.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-authoring-device.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T14:37:28+00:00</t>
+    <t>2025-02-20T14:38:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-authoring-device.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-authoring-device.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T14:38:00+00:00</t>
+    <t>2025-02-20T14:38:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-authoring-device.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-authoring-device.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T14:38:23+00:00</t>
+    <t>2025-02-20T14:42:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-authoring-device.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-authoring-device.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T14:42:14+00:00</t>
+    <t>2025-02-20T14:42:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-authoring-device.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-authoring-device.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T14:42:55+00:00</t>
+    <t>2025-02-20T14:43:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-authoring-device.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-authoring-device.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T14:43:30+00:00</t>
+    <t>2025-02-20T14:45:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-authoring-device.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-authoring-device.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T14:45:32+00:00</t>
+    <t>2025-02-20T14:47:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-authoring-device.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-authoring-device.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T14:47:06+00:00</t>
+    <t>2025-02-20T14:48:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-authoring-device.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-authoring-device.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T14:48:16+00:00</t>
+    <t>2025-02-20T15:31:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-authoring-device.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-authoring-device.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T15:31:18+00:00</t>
+    <t>2025-02-21T13:12:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-authoring-device.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-authoring-device.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-21T13:12:29+00:00</t>
+    <t>2025-02-21T15:18:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-authoring-device.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-authoring-device.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-21T15:18:09+00:00</t>
+    <t>2025-02-23T14:02:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-authoring-device.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-authoring-device.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-23T14:02:58+00:00</t>
+    <t>2025-02-24T10:33:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-authoring-device.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-authoring-device.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-24T10:33:29+00:00</t>
+    <t>2025-02-24T11:08:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-authoring-device.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-authoring-device.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-24T11:08:59+00:00</t>
+    <t>2025-02-24T14:08:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-authoring-device.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-authoring-device.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-24T14:08:41+00:00</t>
+    <t>2025-02-25T09:00:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
